--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260813.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260813.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>12,680,000</t>
+          <t>12,000,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.94%</t>
+          <t>16.05%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.66%</t>
+          <t>6.18%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
@@ -682,95 +682,95 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.11%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>2,040,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.68%</t>
+          <t>4.73%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.65%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>42,300,000</t>
+          <t>1,060,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.14%</t>
+          <t>3.78%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,060,000</t>
+          <t>9,785,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.56%</t>
         </is>
       </c>
     </row>
@@ -792,73 +792,73 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.01%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.75%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -887,44 +887,44 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>4,250,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>4,250,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -953,193 +953,193 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>2,646,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>1,240,000</t>
+          <t>2,190,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,795,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.31%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>462,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.26%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>897,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1254,24 +1254,24 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1283,39 +1283,39 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1359,29 +1359,29 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,010,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,44 +1393,44 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>225,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>225,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -1459,44 +1459,44 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.13%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
@@ -1525,122 +1525,122 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>336,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>150,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.04%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>11,939,092,388</t>
+          <t>13,451,578,932</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-832,613,484</t>
+          <t>3,070,319,573</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
